--- a/kulturarten.xlsx
+++ b/kulturarten.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90792E62-9B36-4A23-9202-489D3FD71640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D444CDA-5335-455A-A394-11EAAF27DCB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17" yWindow="420" windowWidth="32674" windowHeight="17494" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3771" yWindow="1491" windowWidth="17375" windowHeight="16303" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="189">
   <si>
     <t>Kulturart</t>
   </si>
@@ -548,6 +548,45 @@
   </si>
   <si>
     <t>o.garten</t>
+  </si>
+  <si>
+    <t>unbekannt</t>
+  </si>
+  <si>
+    <t>Unbekannt</t>
+  </si>
+  <si>
+    <t>linde</t>
+  </si>
+  <si>
+    <t>flachskuhle</t>
+  </si>
+  <si>
+    <t>lippe=weide</t>
+  </si>
+  <si>
+    <t>binnenweide</t>
+  </si>
+  <si>
+    <t>binnen</t>
+  </si>
+  <si>
+    <t>gärberey</t>
+  </si>
+  <si>
+    <t>binnen weide</t>
+  </si>
+  <si>
+    <t>lagerplatz</t>
+  </si>
+  <si>
+    <t>lache</t>
+  </si>
+  <si>
+    <t>haus &amp; hofraum</t>
+  </si>
+  <si>
+    <t>baustelle</t>
   </si>
 </sst>
 </file>
@@ -603,8 +642,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7FFDC94B-7545-4D51-BF36-506F62FB134A}" name="Tabelle1" displayName="Tabelle1" ref="A1:D155" totalsRowShown="0">
-  <autoFilter ref="A1:D155" xr:uid="{7FFDC94B-7545-4D51-BF36-506F62FB134A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7FFDC94B-7545-4D51-BF36-506F62FB134A}" name="Tabelle1" displayName="Tabelle1" ref="A1:D167" totalsRowShown="0">
+  <autoFilter ref="A1:D167" xr:uid="{7FFDC94B-7545-4D51-BF36-506F62FB134A}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{BC78F5FD-BDA0-49DD-BA3F-9D4976E6B4E6}" name="Kulturart"/>
     <tableColumn id="2" xr3:uid="{E4075862-9F10-4DEF-810C-FA39EC9D4AD7}" name="Kartendarstellung"/>
@@ -878,7 +917,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D155"/>
+  <dimension ref="A1:D167"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="26.84375" bestFit="1" customWidth="1"/>
@@ -1056,18 +1095,18 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>161</v>
       </c>
       <c r="C16" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
         <v>67</v>
@@ -1078,7 +1117,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
         <v>67</v>
@@ -1089,7 +1128,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
         <v>67</v>
@@ -1100,7 +1139,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
         <v>67</v>
@@ -1111,7 +1150,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
         <v>67</v>
@@ -1122,7 +1161,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
         <v>67</v>
@@ -1133,7 +1172,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>187</v>
       </c>
       <c r="B23" t="s">
         <v>67</v>
@@ -1144,7 +1183,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
         <v>67</v>
@@ -1155,7 +1194,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
         <v>67</v>
@@ -1166,7 +1205,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>183</v>
       </c>
       <c r="B26" t="s">
         <v>67</v>
@@ -1177,7 +1216,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B27" t="s">
         <v>67</v>
@@ -1188,7 +1227,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B28" t="s">
         <v>67</v>
@@ -1199,7 +1238,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B29" t="s">
         <v>67</v>
@@ -1210,7 +1249,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B30" t="s">
         <v>67</v>
@@ -1221,7 +1260,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B31" t="s">
         <v>67</v>
@@ -1232,7 +1271,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B32" t="s">
         <v>67</v>
@@ -1243,7 +1282,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B33" t="s">
         <v>67</v>
@@ -1254,7 +1293,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B34" t="s">
         <v>67</v>
@@ -1265,7 +1304,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>185</v>
       </c>
       <c r="B35" t="s">
         <v>67</v>
@@ -1276,7 +1315,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B36" t="s">
         <v>67</v>
@@ -1287,7 +1326,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>173</v>
+        <v>34</v>
       </c>
       <c r="B37" t="s">
         <v>67</v>
@@ -1298,7 +1337,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B38" t="s">
         <v>67</v>
@@ -1309,7 +1348,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B39" t="s">
         <v>67</v>
@@ -1320,7 +1359,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B40" t="s">
         <v>67</v>
@@ -1331,7 +1370,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>173</v>
       </c>
       <c r="B41" t="s">
         <v>67</v>
@@ -1342,7 +1381,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B42" t="s">
         <v>67</v>
@@ -1353,7 +1392,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B43" t="s">
         <v>67</v>
@@ -1364,7 +1403,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
         <v>67</v>
@@ -1375,7 +1414,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B45" t="s">
         <v>67</v>
@@ -1386,7 +1425,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B46" t="s">
         <v>67</v>
@@ -1397,7 +1436,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B47" t="s">
         <v>67</v>
@@ -1408,15 +1447,18 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B48" t="s">
+        <v>67</v>
+      </c>
+      <c r="C48" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B49" t="s">
         <v>67</v>
@@ -1427,7 +1469,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>163</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
         <v>67</v>
@@ -1438,7 +1480,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B51" t="s">
         <v>67</v>
@@ -1449,18 +1491,15 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B52" t="s">
-        <v>67</v>
-      </c>
-      <c r="C52" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B53" t="s">
         <v>67</v>
@@ -1471,50 +1510,59 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>53</v>
+        <v>163</v>
       </c>
       <c r="B54" t="s">
+        <v>67</v>
+      </c>
+      <c r="C54" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B55" t="s">
+        <v>67</v>
+      </c>
+      <c r="C55" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B56" t="s">
+        <v>67</v>
+      </c>
+      <c r="C56" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B57" t="s">
+        <v>67</v>
+      </c>
+      <c r="C57" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B58" t="s">
         <v>67</v>
-      </c>
-      <c r="C58" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B59" t="s">
         <v>67</v>
@@ -1522,7 +1570,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B60" t="s">
         <v>67</v>
@@ -1530,7 +1578,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B61" t="s">
         <v>67</v>
@@ -1538,18 +1586,18 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B62" t="s">
         <v>67</v>
       </c>
       <c r="C62" t="s">
-        <v>67</v>
+        <v>159</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B63" t="s">
         <v>67</v>
@@ -1557,7 +1605,7 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B64" t="s">
         <v>67</v>
@@ -1565,7 +1613,7 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B65" t="s">
         <v>67</v>
@@ -1573,15 +1621,18 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B66" t="s">
+        <v>67</v>
+      </c>
+      <c r="C66" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B67" t="s">
         <v>67</v>
@@ -1589,140 +1640,128 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B68" t="s">
-        <v>162</v>
-      </c>
-      <c r="C68" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B69" t="s">
-        <v>162</v>
+        <v>67</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B70" t="s">
-        <v>162</v>
+        <v>67</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B71" t="s">
-        <v>162</v>
-      </c>
-      <c r="C71" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>73</v>
+        <v>179</v>
       </c>
       <c r="B72" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="B73" t="s">
-        <v>82</v>
+        <v>67</v>
+      </c>
+      <c r="C73" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B74" t="s">
-        <v>82</v>
+        <v>162</v>
+      </c>
+      <c r="C74" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B75" t="s">
-        <v>82</v>
+        <v>162</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B76" t="s">
-        <v>82</v>
+        <v>162</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B77" t="s">
-        <v>82</v>
+        <v>162</v>
       </c>
       <c r="C77" t="s">
-        <v>159</v>
+        <v>72</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="B78" t="s">
         <v>82</v>
       </c>
-      <c r="C78" t="s">
-        <v>159</v>
-      </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>135</v>
+        <v>74</v>
       </c>
       <c r="B79" t="s">
         <v>82</v>
       </c>
-      <c r="C79" t="s">
-        <v>159</v>
-      </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>174</v>
+        <v>75</v>
       </c>
       <c r="B80" t="s">
         <v>82</v>
       </c>
-      <c r="C80" t="s">
-        <v>159</v>
-      </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B81" t="s">
         <v>82</v>
       </c>
-      <c r="C81" t="s">
-        <v>82</v>
-      </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B82" t="s">
         <v>82</v>
@@ -1730,115 +1769,130 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B83" t="s">
         <v>82</v>
       </c>
+      <c r="C83" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B84" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>84</v>
+        <v>135</v>
       </c>
       <c r="B85" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="C85" t="s">
-        <v>98</v>
-      </c>
-      <c r="D85" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B86" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="C86" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B87" t="s">
-        <v>98</v>
+        <v>82</v>
+      </c>
+      <c r="C87" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B88" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B89" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>88</v>
+        <v>180</v>
       </c>
       <c r="B90" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>89</v>
+        <v>181</v>
       </c>
       <c r="B91" t="s">
-        <v>98</v>
+        <v>82</v>
+      </c>
+      <c r="C91" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>90</v>
+        <v>184</v>
       </c>
       <c r="B92" t="s">
-        <v>98</v>
+        <v>82</v>
+      </c>
+      <c r="C92" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>92</v>
+        <v>182</v>
       </c>
       <c r="B93" t="s">
-        <v>98</v>
+        <v>82</v>
+      </c>
+      <c r="C93" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="B94" t="s">
         <v>98</v>
       </c>
+      <c r="C94" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B95" t="s">
         <v>98</v>
@@ -1846,202 +1900,178 @@
       <c r="C95" t="s">
         <v>98</v>
       </c>
+      <c r="D95" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>96</v>
+        <v>171</v>
       </c>
       <c r="B96" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C96" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="B97" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
-        <v>165</v>
+        <v>86</v>
       </c>
       <c r="B98" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
+        <v>87</v>
+      </c>
+      <c r="B99" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A100" t="s">
+        <v>88</v>
+      </c>
+      <c r="B100" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A101" t="s">
+        <v>89</v>
+      </c>
+      <c r="B101" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A102" t="s">
+        <v>90</v>
+      </c>
+      <c r="B102" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A103" t="s">
+        <v>92</v>
+      </c>
+      <c r="B103" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A104" t="s">
+        <v>93</v>
+      </c>
+      <c r="B104" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A105" t="s">
+        <v>94</v>
+      </c>
+      <c r="B105" t="s">
+        <v>98</v>
+      </c>
+      <c r="C105" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A106" t="s">
+        <v>96</v>
+      </c>
+      <c r="B106" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A107" t="s">
+        <v>97</v>
+      </c>
+      <c r="B107" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A108" t="s">
+        <v>165</v>
+      </c>
+      <c r="B108" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A109" t="s">
         <v>99</v>
-      </c>
-      <c r="B99" t="s">
-        <v>114</v>
-      </c>
-      <c r="C99" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A100" t="s">
-        <v>100</v>
-      </c>
-      <c r="B100" t="s">
-        <v>114</v>
-      </c>
-      <c r="C100" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A101" t="s">
-        <v>101</v>
-      </c>
-      <c r="B101" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A102" t="s">
-        <v>102</v>
-      </c>
-      <c r="B102" t="s">
-        <v>114</v>
-      </c>
-      <c r="C102" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A103" t="s">
-        <v>103</v>
-      </c>
-      <c r="B103" t="s">
-        <v>114</v>
-      </c>
-      <c r="C103" t="s">
-        <v>115</v>
-      </c>
-      <c r="D103" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A104" t="s">
-        <v>104</v>
-      </c>
-      <c r="B104" t="s">
-        <v>114</v>
-      </c>
-      <c r="C104" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A105" t="s">
-        <v>105</v>
-      </c>
-      <c r="B105" t="s">
-        <v>114</v>
-      </c>
-      <c r="C105" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A106" t="s">
-        <v>91</v>
-      </c>
-      <c r="B106" t="s">
-        <v>114</v>
-      </c>
-      <c r="C106" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A107" t="s">
-        <v>106</v>
-      </c>
-      <c r="B107" t="s">
-        <v>114</v>
-      </c>
-      <c r="C107" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A108" t="s">
-        <v>166</v>
-      </c>
-      <c r="B108" t="s">
-        <v>114</v>
-      </c>
-      <c r="C108" t="s">
-        <v>116</v>
-      </c>
-      <c r="D108" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A109" t="s">
-        <v>175</v>
       </c>
       <c r="B109" t="s">
         <v>114</v>
       </c>
       <c r="C109" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.4">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B110" t="s">
         <v>114</v>
       </c>
       <c r="C110" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.4">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="B111" t="s">
         <v>114</v>
       </c>
-      <c r="C111" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.4">
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="B112" t="s">
         <v>114</v>
       </c>
       <c r="C112" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.4">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="B113" t="s">
         <v>114</v>
       </c>
       <c r="C113" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.4">
+        <v>115</v>
+      </c>
+      <c r="D113" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B114" t="s">
         <v>114</v>
@@ -2050,9 +2080,9 @@
         <v>115</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B115" t="s">
         <v>114</v>
@@ -2061,9 +2091,9 @@
         <v>115</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="B116" t="s">
         <v>114</v>
@@ -2072,234 +2102,237 @@
         <v>115</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B117" t="s">
         <v>114</v>
       </c>
       <c r="C117" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.4">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
-        <v>113</v>
+        <v>166</v>
       </c>
       <c r="B118" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C118" t="s">
+        <v>116</v>
+      </c>
+      <c r="D118" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
-        <v>117</v>
+        <v>175</v>
       </c>
       <c r="B119" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.4">
+        <v>114</v>
+      </c>
+      <c r="C119" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="B120" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.4">
+        <v>114</v>
+      </c>
+      <c r="C120" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>32</v>
+        <v>108</v>
       </c>
       <c r="B121" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.4">
+        <v>114</v>
+      </c>
+      <c r="C121" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="B122" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.4">
+        <v>114</v>
+      </c>
+      <c r="C122" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="B123" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.4">
+        <v>114</v>
+      </c>
+      <c r="C123" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
-        <v>121</v>
+        <v>178</v>
       </c>
       <c r="B124" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.4">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="B125" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.4">
+        <v>114</v>
+      </c>
+      <c r="C125" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="B126" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.4">
+        <v>114</v>
+      </c>
+      <c r="C126" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="B127" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.4">
+        <v>114</v>
+      </c>
+      <c r="C127" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A128" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="B128" t="s">
-        <v>127</v>
+        <v>114</v>
+      </c>
+      <c r="C128" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B129" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="B130" t="s">
-        <v>145</v>
-      </c>
-      <c r="C130" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="B131" t="s">
-        <v>145</v>
-      </c>
-      <c r="C131" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
-        <v>130</v>
+        <v>32</v>
       </c>
       <c r="B132" t="s">
-        <v>145</v>
-      </c>
-      <c r="C132" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="B133" t="s">
-        <v>145</v>
-      </c>
-      <c r="C133" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B134" t="s">
-        <v>145</v>
-      </c>
-      <c r="C134" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A135" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="B135" t="s">
-        <v>145</v>
-      </c>
-      <c r="C135" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="B136" t="s">
-        <v>145</v>
-      </c>
-      <c r="C136" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="B137" t="s">
-        <v>145</v>
-      </c>
-      <c r="C137" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A138" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="B138" t="s">
-        <v>145</v>
-      </c>
-      <c r="C138" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A139" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="B139" t="s">
-        <v>145</v>
-      </c>
-      <c r="C139" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A140" t="s">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="B140" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A141" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="B141" t="s">
         <v>145</v>
@@ -2310,7 +2343,7 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A142" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="B142" t="s">
         <v>145</v>
@@ -2321,127 +2354,253 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="B143" t="s">
         <v>145</v>
       </c>
+      <c r="C143" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="B144" t="s">
         <v>145</v>
       </c>
+      <c r="C144" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A145" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="B145" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="C145" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A146" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="B146" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="C146" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="B147" t="s">
-        <v>157</v>
+        <v>145</v>
+      </c>
+      <c r="C147" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="B148" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="C148" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A149" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="B149" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="C149" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="B150" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="C150" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B151" t="s">
-        <v>157</v>
-      </c>
-      <c r="C151" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A152" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="B152" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="C152" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="B153" t="s">
-        <v>157</v>
+        <v>145</v>
+      </c>
+      <c r="C153" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="B154" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A155" t="s">
+        <v>144</v>
+      </c>
+      <c r="B155" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A156" t="s">
+        <v>146</v>
+      </c>
+      <c r="B156" t="s">
+        <v>157</v>
+      </c>
+      <c r="C156" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A157" t="s">
+        <v>147</v>
+      </c>
+      <c r="B157" t="s">
+        <v>157</v>
+      </c>
+      <c r="C157" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A158" t="s">
+        <v>148</v>
+      </c>
+      <c r="B158" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A159" t="s">
+        <v>149</v>
+      </c>
+      <c r="B159" t="s">
+        <v>157</v>
+      </c>
+      <c r="C159" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A160" t="s">
+        <v>150</v>
+      </c>
+      <c r="B160" t="s">
+        <v>157</v>
+      </c>
+      <c r="C160" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A161" t="s">
+        <v>151</v>
+      </c>
+      <c r="B161" t="s">
+        <v>157</v>
+      </c>
+      <c r="C161" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A162" t="s">
+        <v>152</v>
+      </c>
+      <c r="B162" t="s">
+        <v>157</v>
+      </c>
+      <c r="C162" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A163" t="s">
+        <v>153</v>
+      </c>
+      <c r="B163" t="s">
+        <v>157</v>
+      </c>
+      <c r="C163" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A164" t="s">
+        <v>154</v>
+      </c>
+      <c r="B164" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A165" t="s">
+        <v>155</v>
+      </c>
+      <c r="B165" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A166" t="s">
         <v>156</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B166" t="s">
         <v>157</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A167" t="s">
+        <v>176</v>
+      </c>
+      <c r="B167" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/kulturarten.xlsx
+++ b/kulturarten.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D444CDA-5335-455A-A394-11EAAF27DCB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE066280-7B83-45EC-959D-344B60AF71BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3771" yWindow="1491" windowWidth="17375" windowHeight="16303" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="191">
   <si>
     <t>Kulturart</t>
   </si>
@@ -587,6 +587,12 @@
   </si>
   <si>
     <t>baustelle</t>
+  </si>
+  <si>
+    <t>haus &amp; baustelle</t>
+  </si>
+  <si>
+    <t>haus ohne grund</t>
   </si>
 </sst>
 </file>
@@ -642,8 +648,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7FFDC94B-7545-4D51-BF36-506F62FB134A}" name="Tabelle1" displayName="Tabelle1" ref="A1:D167" totalsRowShown="0">
-  <autoFilter ref="A1:D167" xr:uid="{7FFDC94B-7545-4D51-BF36-506F62FB134A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7FFDC94B-7545-4D51-BF36-506F62FB134A}" name="Tabelle1" displayName="Tabelle1" ref="A1:D169" totalsRowShown="0">
+  <autoFilter ref="A1:D169" xr:uid="{7FFDC94B-7545-4D51-BF36-506F62FB134A}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{BC78F5FD-BDA0-49DD-BA3F-9D4976E6B4E6}" name="Kulturart"/>
     <tableColumn id="2" xr3:uid="{E4075862-9F10-4DEF-810C-FA39EC9D4AD7}" name="Kartendarstellung"/>
@@ -917,7 +923,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D167"/>
+  <dimension ref="A1:D169"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="26.84375" bestFit="1" customWidth="1"/>
@@ -1183,7 +1189,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>189</v>
       </c>
       <c r="B24" t="s">
         <v>67</v>
@@ -1194,7 +1200,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>190</v>
       </c>
       <c r="B25" t="s">
         <v>67</v>
@@ -1205,7 +1211,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>183</v>
+        <v>22</v>
       </c>
       <c r="B26" t="s">
         <v>67</v>
@@ -1216,7 +1222,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27" t="s">
         <v>67</v>
@@ -1227,7 +1233,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>25</v>
+        <v>183</v>
       </c>
       <c r="B28" t="s">
         <v>67</v>
@@ -1238,7 +1244,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B29" t="s">
         <v>67</v>
@@ -1249,7 +1255,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B30" t="s">
         <v>67</v>
@@ -1260,7 +1266,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B31" t="s">
         <v>67</v>
@@ -1271,7 +1277,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B32" t="s">
         <v>67</v>
@@ -1282,7 +1288,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B33" t="s">
         <v>67</v>
@@ -1293,7 +1299,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B34" t="s">
         <v>67</v>
@@ -1304,7 +1310,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>185</v>
+        <v>30</v>
       </c>
       <c r="B35" t="s">
         <v>67</v>
@@ -1315,7 +1321,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B36" t="s">
         <v>67</v>
@@ -1326,7 +1332,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>34</v>
+        <v>185</v>
       </c>
       <c r="B37" t="s">
         <v>67</v>
@@ -1337,7 +1343,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B38" t="s">
         <v>67</v>
@@ -1348,7 +1354,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B39" t="s">
         <v>67</v>
@@ -1359,7 +1365,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B40" t="s">
         <v>67</v>
@@ -1370,7 +1376,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>173</v>
+        <v>36</v>
       </c>
       <c r="B41" t="s">
         <v>67</v>
@@ -1381,7 +1387,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B42" t="s">
         <v>67</v>
@@ -1392,7 +1398,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>39</v>
+        <v>173</v>
       </c>
       <c r="B43" t="s">
         <v>67</v>
@@ -1403,7 +1409,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B44" t="s">
         <v>67</v>
@@ -1414,7 +1420,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B45" t="s">
         <v>67</v>
@@ -1425,7 +1431,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
         <v>67</v>
@@ -1436,7 +1442,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B47" t="s">
         <v>67</v>
@@ -1447,7 +1453,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B48" t="s">
         <v>67</v>
@@ -1458,7 +1464,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B49" t="s">
         <v>67</v>
@@ -1469,7 +1475,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B50" t="s">
         <v>67</v>
@@ -1480,7 +1486,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B51" t="s">
         <v>67</v>
@@ -1491,15 +1497,18 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B52" t="s">
+        <v>67</v>
+      </c>
+      <c r="C52" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B53" t="s">
         <v>67</v>
@@ -1510,18 +1519,15 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>163</v>
+        <v>48</v>
       </c>
       <c r="B54" t="s">
-        <v>67</v>
-      </c>
-      <c r="C54" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B55" t="s">
         <v>67</v>
@@ -1532,7 +1538,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>51</v>
+        <v>163</v>
       </c>
       <c r="B56" t="s">
         <v>67</v>
@@ -1543,7 +1549,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B57" t="s">
         <v>67</v>
@@ -1554,23 +1560,29 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B58" t="s">
+        <v>67</v>
+      </c>
+      <c r="C58" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B59" t="s">
+        <v>67</v>
+      </c>
+      <c r="C59" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B60" t="s">
         <v>67</v>
@@ -1578,7 +1590,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B61" t="s">
         <v>67</v>
@@ -1586,18 +1598,15 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B62" t="s">
         <v>67</v>
-      </c>
-      <c r="C62" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B63" t="s">
         <v>67</v>
@@ -1605,15 +1614,18 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B64" t="s">
         <v>67</v>
+      </c>
+      <c r="C64" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B65" t="s">
         <v>67</v>
@@ -1621,18 +1633,15 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B66" t="s">
-        <v>67</v>
-      </c>
-      <c r="C66" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B67" t="s">
         <v>67</v>
@@ -1640,15 +1649,18 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B68" t="s">
+        <v>67</v>
+      </c>
+      <c r="C68" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B69" t="s">
         <v>67</v>
@@ -1656,7 +1668,7 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B70" t="s">
         <v>67</v>
@@ -1664,7 +1676,7 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B71" t="s">
         <v>67</v>
@@ -1672,7 +1684,7 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>179</v>
+        <v>65</v>
       </c>
       <c r="B72" t="s">
         <v>67</v>
@@ -1680,118 +1692,112 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>188</v>
+        <v>66</v>
       </c>
       <c r="B73" t="s">
-        <v>67</v>
-      </c>
-      <c r="C73" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>68</v>
+        <v>179</v>
       </c>
       <c r="B74" t="s">
-        <v>162</v>
-      </c>
-      <c r="C74" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>69</v>
+        <v>188</v>
       </c>
       <c r="B75" t="s">
-        <v>162</v>
+        <v>67</v>
+      </c>
+      <c r="C75" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B76" t="s">
         <v>162</v>
       </c>
+      <c r="C76" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B77" t="s">
         <v>162</v>
       </c>
-      <c r="C77" t="s">
-        <v>72</v>
-      </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B78" t="s">
-        <v>82</v>
+        <v>162</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B79" t="s">
-        <v>82</v>
+        <v>162</v>
+      </c>
+      <c r="C79" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B80" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B81" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B82" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B83" t="s">
         <v>82</v>
       </c>
-      <c r="C83" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.4">
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B84" t="s">
         <v>82</v>
       </c>
-      <c r="C84" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.4">
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="B85" t="s">
         <v>82</v>
@@ -1800,9 +1806,9 @@
         <v>159</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>174</v>
+        <v>95</v>
       </c>
       <c r="B86" t="s">
         <v>82</v>
@@ -1811,66 +1817,66 @@
         <v>159</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="B87" t="s">
         <v>82</v>
       </c>
       <c r="C87" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.4">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="B88" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C88" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B89" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C89" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="B90" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>181</v>
+        <v>81</v>
       </c>
       <c r="B91" t="s">
         <v>82</v>
       </c>
-      <c r="C91" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.4">
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B92" t="s">
         <v>82</v>
       </c>
-      <c r="C92" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.4">
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B93" t="s">
         <v>82</v>
@@ -1879,34 +1885,31 @@
         <v>82</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
+        <v>184</v>
+      </c>
+      <c r="B94" t="s">
+        <v>82</v>
+      </c>
+      <c r="C94" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A95" t="s">
+        <v>182</v>
+      </c>
+      <c r="B95" t="s">
+        <v>82</v>
+      </c>
+      <c r="C95" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A96" t="s">
         <v>83</v>
-      </c>
-      <c r="B94" t="s">
-        <v>98</v>
-      </c>
-      <c r="C94" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A95" t="s">
-        <v>84</v>
-      </c>
-      <c r="B95" t="s">
-        <v>98</v>
-      </c>
-      <c r="C95" t="s">
-        <v>98</v>
-      </c>
-      <c r="D95" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A96" t="s">
-        <v>171</v>
       </c>
       <c r="B96" t="s">
         <v>98</v>
@@ -1915,138 +1918,144 @@
         <v>98</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B97" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C97" t="s">
+        <v>98</v>
+      </c>
+      <c r="D97" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
-        <v>86</v>
+        <v>171</v>
       </c>
       <c r="B98" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C98" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B99" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B100" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B101" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B102" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B103" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B104" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B105" t="s">
         <v>98</v>
       </c>
-      <c r="C105" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B106" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B107" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C107" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
-        <v>165</v>
+        <v>96</v>
       </c>
       <c r="B108" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
+        <v>97</v>
+      </c>
+      <c r="B109" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A110" t="s">
+        <v>165</v>
+      </c>
+      <c r="B110" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A111" t="s">
         <v>99</v>
-      </c>
-      <c r="B109" t="s">
-        <v>114</v>
-      </c>
-      <c r="C109" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A110" t="s">
-        <v>100</v>
-      </c>
-      <c r="B110" t="s">
-        <v>114</v>
-      </c>
-      <c r="C110" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A111" t="s">
-        <v>101</v>
       </c>
       <c r="B111" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C111" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B112" t="s">
         <v>114</v>
@@ -2057,21 +2066,15 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B113" t="s">
         <v>114</v>
       </c>
-      <c r="C113" t="s">
-        <v>115</v>
-      </c>
-      <c r="D113" t="s">
-        <v>168</v>
-      </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B114" t="s">
         <v>114</v>
@@ -2082,7 +2085,7 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B115" t="s">
         <v>114</v>
@@ -2090,10 +2093,13 @@
       <c r="C115" t="s">
         <v>115</v>
       </c>
+      <c r="D115" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="B116" t="s">
         <v>114</v>
@@ -2104,32 +2110,29 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B117" t="s">
         <v>114</v>
       </c>
       <c r="C117" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
-        <v>166</v>
+        <v>91</v>
       </c>
       <c r="B118" t="s">
         <v>114</v>
       </c>
       <c r="C118" t="s">
-        <v>116</v>
-      </c>
-      <c r="D118" t="s">
-        <v>169</v>
+        <v>115</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
-        <v>175</v>
+        <v>106</v>
       </c>
       <c r="B119" t="s">
         <v>114</v>
@@ -2140,7 +2143,7 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>107</v>
+        <v>166</v>
       </c>
       <c r="B120" t="s">
         <v>114</v>
@@ -2148,10 +2151,13 @@
       <c r="C120" t="s">
         <v>116</v>
       </c>
+      <c r="D120" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>108</v>
+        <v>175</v>
       </c>
       <c r="B121" t="s">
         <v>114</v>
@@ -2162,7 +2168,7 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="B122" t="s">
         <v>114</v>
@@ -2173,7 +2179,7 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="B123" t="s">
         <v>114</v>
@@ -2184,37 +2190,37 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
-        <v>178</v>
+        <v>139</v>
       </c>
       <c r="B124" t="s">
         <v>114</v>
       </c>
+      <c r="C124" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="B125" t="s">
         <v>114</v>
       </c>
       <c r="C125" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
-        <v>110</v>
+        <v>178</v>
       </c>
       <c r="B126" t="s">
         <v>114</v>
       </c>
-      <c r="C126" t="s">
-        <v>115</v>
-      </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B127" t="s">
         <v>114</v>
@@ -2225,7 +2231,7 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A128" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B128" t="s">
         <v>114</v>
@@ -2236,31 +2242,37 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B129" t="s">
         <v>114</v>
       </c>
+      <c r="C129" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B130" t="s">
-        <v>127</v>
+        <v>114</v>
+      </c>
+      <c r="C130" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B131" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="B132" t="s">
         <v>127</v>
@@ -2268,7 +2280,7 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B133" t="s">
         <v>127</v>
@@ -2276,7 +2288,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="B134" t="s">
         <v>127</v>
@@ -2284,7 +2296,7 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A135" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B135" t="s">
         <v>127</v>
@@ -2292,7 +2304,7 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B136" t="s">
         <v>127</v>
@@ -2300,7 +2312,7 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B137" t="s">
         <v>127</v>
@@ -2308,7 +2320,7 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A138" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B138" t="s">
         <v>127</v>
@@ -2316,7 +2328,7 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A139" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B139" t="s">
         <v>127</v>
@@ -2324,7 +2336,7 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A140" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B140" t="s">
         <v>127</v>
@@ -2332,29 +2344,23 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A141" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B141" t="s">
-        <v>145</v>
-      </c>
-      <c r="C141" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A142" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B142" t="s">
-        <v>145</v>
-      </c>
-      <c r="C142" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B143" t="s">
         <v>145</v>
@@ -2365,7 +2371,7 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B144" t="s">
         <v>145</v>
@@ -2376,7 +2382,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A145" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B145" t="s">
         <v>145</v>
@@ -2387,7 +2393,7 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A146" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B146" t="s">
         <v>145</v>
@@ -2398,7 +2404,7 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B147" t="s">
         <v>145</v>
@@ -2409,7 +2415,7 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B148" t="s">
         <v>145</v>
@@ -2420,7 +2426,7 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A149" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B149" t="s">
         <v>145</v>
@@ -2431,7 +2437,7 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B150" t="s">
         <v>145</v>
@@ -2442,15 +2448,18 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="B151" t="s">
         <v>145</v>
       </c>
+      <c r="C151" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A152" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B152" t="s">
         <v>145</v>
@@ -2461,64 +2470,64 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="B153" t="s">
         <v>145</v>
       </c>
-      <c r="C153" t="s">
-        <v>145</v>
-      </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B154" t="s">
         <v>145</v>
       </c>
+      <c r="C154" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A155" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B155" t="s">
         <v>145</v>
       </c>
+      <c r="C155" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A156" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B156" t="s">
-        <v>157</v>
-      </c>
-      <c r="C156" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A157" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B157" t="s">
-        <v>157</v>
-      </c>
-      <c r="C157" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A158" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B158" t="s">
         <v>157</v>
       </c>
+      <c r="C158" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A159" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B159" t="s">
         <v>157</v>
@@ -2529,18 +2538,15 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A160" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B160" t="s">
         <v>157</v>
       </c>
-      <c r="C160" t="s">
-        <v>160</v>
-      </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B161" t="s">
         <v>157</v>
@@ -2551,7 +2557,7 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A162" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B162" t="s">
         <v>157</v>
@@ -2562,7 +2568,7 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A163" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B163" t="s">
         <v>157</v>
@@ -2573,23 +2579,29 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A164" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B164" t="s">
         <v>157</v>
       </c>
+      <c r="C164" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A165" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B165" t="s">
         <v>157</v>
       </c>
+      <c r="C165" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A166" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B166" t="s">
         <v>157</v>
@@ -2597,9 +2609,25 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A167" t="s">
+        <v>155</v>
+      </c>
+      <c r="B167" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A168" t="s">
+        <v>156</v>
+      </c>
+      <c r="B168" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A169" t="s">
         <v>176</v>
       </c>
-      <c r="B167" t="s">
+      <c r="B169" t="s">
         <v>177</v>
       </c>
     </row>

--- a/kulturarten.xlsx
+++ b/kulturarten.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE066280-7B83-45EC-959D-344B60AF71BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE89D97-3470-4DF6-88EC-023C3C085944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3771" yWindow="1491" windowWidth="17375" windowHeight="16303" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="191">
   <si>
     <t>Kulturart</t>
   </si>
@@ -1646,6 +1646,9 @@
       <c r="B67" t="s">
         <v>67</v>
       </c>
+      <c r="C67" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A68" t="s">

--- a/kulturarten.xlsx
+++ b/kulturarten.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE89D97-3470-4DF6-88EC-023C3C085944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8723593-1F8A-464F-BE0E-ECAEB360064F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="192">
   <si>
     <t>Kulturart</t>
   </si>
@@ -593,6 +593,9 @@
   </si>
   <si>
     <t>haus ohne grund</t>
+  </si>
+  <si>
+    <t>Hütung;Clarholz=Heide</t>
   </si>
 </sst>
 </file>
@@ -1817,7 +1820,7 @@
         <v>82</v>
       </c>
       <c r="C86" t="s">
-        <v>159</v>
+        <v>191</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.4">

--- a/kulturarten.xlsx
+++ b/kulturarten.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8723593-1F8A-464F-BE0E-ECAEB360064F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE117BF5-79E2-4B17-A4EE-9A68CE78C3D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="193">
   <si>
     <t>Kulturart</t>
   </si>
@@ -596,6 +596,9 @@
   </si>
   <si>
     <t>Hütung;Clarholz=Heide</t>
+  </si>
+  <si>
+    <t>Öde</t>
   </si>
 </sst>
 </file>
@@ -1110,7 +1113,7 @@
         <v>161</v>
       </c>
       <c r="C16" t="s">
-        <v>15</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.4">
